--- a/survey_templates/030_preventive_health_engagement_survey--survey_templates.xlsx
+++ b/survey_templates/030_preventive_health_engagement_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_20,000'}</t>
+          <t>less_than_20,000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Less than 20,000'}</t>
+          <t>Less than 20,000</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'20,000-40,000'}</t>
+          <t>20,000-40,000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '20,000-40,000'}</t>
+          <t>20,000-40,000</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'more_than_40,000'}</t>
+          <t>more_than_40,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'More than 40,000'}</t>
+          <t>More than 40,000</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_exercise_regularly'}</t>
+          <t>i_exercise_regularly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I exercise regularly'}</t>
+          <t>I exercise regularly</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'i_eat_a_balanced_diet'}</t>
+          <t>i_eat_a_balanced_diet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'I eat a balanced diet'}</t>
+          <t>I eat a balanced diet</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'i_get_enough_sleep'}</t>
+          <t>i_get_enough_sleep</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'I get enough sleep'}</t>
+          <t>I get enough sleep</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'i_take_care_of_my_mental_health'}</t>
+          <t>i_take_care_of_my_mental_health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'I take care of my mental health'}</t>
+          <t>I take care of my mental health</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'i_get_regular_check-ups'}</t>
+          <t>i_get_regular_check-ups</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'I get regular check-ups'}</t>
+          <t>I get regular check-ups</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'i_practice_stress_management'}</t>
+          <t>i_practice_stress_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'I practice stress management'}</t>
+          <t>I practice stress management</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'i_use_relaxation_techniques'}</t>
+          <t>i_use_relaxation_techniques</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'I use relaxation techniques'}</t>
+          <t>I use relaxation techniques</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'i_take_my_medications_as_prescribed'}</t>
+          <t>i_take_my_medications_as_prescribed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'I take my medications as prescribed'}</t>
+          <t>I take my medications as prescribed</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'i_have_a_healthy_relationship_with_food'}</t>
+          <t>i_have_a_healthy_relationship_with_food</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'I have a healthy relationship with food'}</t>
+          <t>I have a healthy relationship with food</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'i_engage_in_physical_activity'}</t>
+          <t>i_engage_in_physical_activity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'I engage in physical activity'}</t>
+          <t>I engage in physical activity</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'i_get_vaccinated'}</t>
+          <t>i_get_vaccinated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'I get vaccinated'}</t>
+          <t>I get vaccinated</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'i_have_a_healthy_relationship_with_substances'}</t>
+          <t>i_have_a_healthy_relationship_with_substances</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'I have a healthy relationship with substances'}</t>
+          <t>I have a healthy relationship with substances</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_am_motivated_to_make_healthy_changes'}</t>
+          <t>i_am_motivated_to_make_healthy_changes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I am motivated to make healthy changes'}</t>
+          <t>I am motivated to make healthy changes</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'i_am_confident_in_my_abilities'}</t>
+          <t>i_am_confident_in_my_abilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'I am confident in my abilities'}</t>
+          <t>I am confident in my abilities</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'i_am_willing_to_make_changes_to_improve_my_health'}</t>
+          <t>i_am_willing_to_make_changes_to_improve_my_health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'I am willing to make changes to improve my health'}</t>
+          <t>I am willing to make changes to improve my health</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'i_have_the_knowledge_to_make_healthy_choices'}</t>
+          <t>i_have_the_knowledge_to_make_healthy_choices</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'I have the knowledge to make healthy choices'}</t>
+          <t>I have the knowledge to make healthy choices</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'i_have_the_resources_to_make_healthy_changes'}</t>
+          <t>i_have_the_resources_to_make_healthy_changes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'I have the resources to make healthy changes'}</t>
+          <t>I have the resources to make healthy changes</t>
         </is>
       </c>
     </row>
